--- a/outputs/master_rename_build/tables/mixed_dimension_items.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_items.xlsx
@@ -13,12 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10" uniqueCount="10">
   <si>
     <t>pull_item</t>
-  </si>
-  <si>
-    <t>beer</t>
   </si>
   <si>
     <t>chicken</t>
@@ -37,9 +34,6 @@
   </si>
   <si>
     <t>loaf bread</t>
-  </si>
-  <si>
-    <t>mineral or spring water, all drinking water sold in containers</t>
   </si>
   <si>
     <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
@@ -94,7 +88,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102,10 +96,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -113,7 +107,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>4</v>
+        <v>846</v>
       </c>
       <c r="C2" s="1">
         <v>2</v>
@@ -124,10 +118,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>846</v>
+        <v>1081</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -135,10 +129,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1082</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
-        <v>4</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -146,10 +140,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="C5" s="1">
-        <v>164</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6">
@@ -157,10 +151,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>324</v>
+        <v>251</v>
       </c>
       <c r="C6" s="1">
-        <v>554</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7">
@@ -168,10 +162,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>254</v>
+        <v>1045</v>
       </c>
       <c r="C7" s="1">
-        <v>875</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -179,31 +173,9 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1045</v>
+        <v>947</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>947</v>
-      </c>
-      <c r="C10" s="1">
         <v>5</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/mixed_dimension_items.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_items.xlsx
@@ -143,7 +143,7 @@
         <v>324</v>
       </c>
       <c r="C5" s="1">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6">
@@ -151,7 +151,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C6" s="1">
         <v>874</v>
